--- a/kenyan-hardware-demo-inventory.xlsx
+++ b/kenyan-hardware-demo-inventory.xlsx
@@ -1,10 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10726"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46A55C7-FC53-6F4F-9EFA-B7CFDC7F7EB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="33600" windowHeight="19200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Products" state="visible" r:id="rId4"/>
+    <sheet name="Products" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -3415,17 +3419,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -3789,9 +3795,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I372"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3802,7 +3808,7 @@
     <col min="8" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3831,7 +3837,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3851,7 +3857,7 @@
         <v>6335</v>
       </c>
       <c r="G2">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>16</v>
@@ -3860,7 +3866,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -3880,7 +3886,7 @@
         <v>4585</v>
       </c>
       <c r="G3">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>6</v>
@@ -3889,7 +3895,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3909,7 +3915,7 @@
         <v>6015</v>
       </c>
       <c r="G4">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H4">
         <v>18</v>
@@ -3918,7 +3924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -3938,7 +3944,7 @@
         <v>3420</v>
       </c>
       <c r="G5">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>8</v>
@@ -3947,7 +3953,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3967,7 +3973,7 @@
         <v>5260</v>
       </c>
       <c r="G6">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H6">
         <v>18</v>
@@ -3976,7 +3982,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -3996,7 +4002,7 @@
         <v>7140</v>
       </c>
       <c r="G7">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -4005,7 +4011,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -4025,7 +4031,7 @@
         <v>3470</v>
       </c>
       <c r="G8">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>6</v>
@@ -4034,7 +4040,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -4054,7 +4060,7 @@
         <v>1625</v>
       </c>
       <c r="G9">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H9">
         <v>16</v>
@@ -4063,7 +4069,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>34</v>
       </c>
@@ -4083,7 +4089,7 @@
         <v>5310</v>
       </c>
       <c r="G10">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>14</v>
@@ -4092,7 +4098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>37</v>
       </c>
@@ -4112,7 +4118,7 @@
         <v>7205</v>
       </c>
       <c r="G11">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -4121,7 +4127,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -4141,7 +4147,7 @@
         <v>7245</v>
       </c>
       <c r="G12">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>6</v>
@@ -4150,7 +4156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -4170,7 +4176,7 @@
         <v>7995</v>
       </c>
       <c r="G13">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H13">
         <v>15</v>
@@ -4179,7 +4185,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -4199,7 +4205,7 @@
         <v>8010</v>
       </c>
       <c r="G14">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -4208,7 +4214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -4228,7 +4234,7 @@
         <v>5035</v>
       </c>
       <c r="G15">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H15">
         <v>6</v>
@@ -4237,7 +4243,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>52</v>
       </c>
@@ -4257,7 +4263,7 @@
         <v>5555</v>
       </c>
       <c r="G16">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>12</v>
@@ -4266,7 +4272,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -4286,7 +4292,7 @@
         <v>1295</v>
       </c>
       <c r="G17">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H17">
         <v>19</v>
@@ -4295,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -4315,7 +4321,7 @@
         <v>9430</v>
       </c>
       <c r="G18">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H18">
         <v>11</v>
@@ -4324,7 +4330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -4344,7 +4350,7 @@
         <v>3510</v>
       </c>
       <c r="G19">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H19">
         <v>17</v>
@@ -4353,7 +4359,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -4373,7 +4379,7 @@
         <v>6320</v>
       </c>
       <c r="G20">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>16</v>
@@ -4382,7 +4388,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -4402,7 +4408,7 @@
         <v>2085</v>
       </c>
       <c r="G21">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H21">
         <v>9</v>
@@ -4411,7 +4417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -4431,7 +4437,7 @@
         <v>4635</v>
       </c>
       <c r="G22">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>16</v>
@@ -4440,7 +4446,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -4460,7 +4466,7 @@
         <v>5285</v>
       </c>
       <c r="G23">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H23">
         <v>7</v>
@@ -4469,7 +4475,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -4489,7 +4495,7 @@
         <v>3060</v>
       </c>
       <c r="G24">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H24">
         <v>19</v>
@@ -4498,7 +4504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>79</v>
       </c>
@@ -4518,7 +4524,7 @@
         <v>4320</v>
       </c>
       <c r="G25">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H25">
         <v>14</v>
@@ -4527,7 +4533,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>82</v>
       </c>
@@ -4547,7 +4553,7 @@
         <v>8070</v>
       </c>
       <c r="G26">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H26">
         <v>14</v>
@@ -4556,7 +4562,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>85</v>
       </c>
@@ -4576,7 +4582,7 @@
         <v>1125</v>
       </c>
       <c r="G27">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H27">
         <v>7</v>
@@ -4585,7 +4591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>88</v>
       </c>
@@ -4605,7 +4611,7 @@
         <v>5545</v>
       </c>
       <c r="G28">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>7</v>
@@ -4614,7 +4620,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -4634,7 +4640,7 @@
         <v>7250</v>
       </c>
       <c r="G29">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H29">
         <v>8</v>
@@ -4643,7 +4649,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>94</v>
       </c>
@@ -4663,7 +4669,7 @@
         <v>8515</v>
       </c>
       <c r="G30">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H30">
         <v>17</v>
@@ -4672,7 +4678,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -4692,7 +4698,7 @@
         <v>1360</v>
       </c>
       <c r="G31">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H31">
         <v>15</v>
@@ -4701,7 +4707,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>100</v>
       </c>
@@ -4721,7 +4727,7 @@
         <v>6465</v>
       </c>
       <c r="G32">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>15</v>
@@ -4730,7 +4736,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>103</v>
       </c>
@@ -4750,7 +4756,7 @@
         <v>7890</v>
       </c>
       <c r="G33">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H33">
         <v>6</v>
@@ -4759,7 +4765,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>106</v>
       </c>
@@ -4779,7 +4785,7 @@
         <v>5470</v>
       </c>
       <c r="G34">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H34">
         <v>17</v>
@@ -4788,7 +4794,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>109</v>
       </c>
@@ -4808,7 +4814,7 @@
         <v>4155</v>
       </c>
       <c r="G35">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H35">
         <v>15</v>
@@ -4817,7 +4823,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -4837,7 +4843,7 @@
         <v>765</v>
       </c>
       <c r="G36">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H36">
         <v>6</v>
@@ -4846,7 +4852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>115</v>
       </c>
@@ -4866,7 +4872,7 @@
         <v>2665</v>
       </c>
       <c r="G37">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H37">
         <v>14</v>
@@ -4875,7 +4881,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>118</v>
       </c>
@@ -4895,7 +4901,7 @@
         <v>2515</v>
       </c>
       <c r="G38">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H38">
         <v>19</v>
@@ -4904,7 +4910,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>121</v>
       </c>
@@ -4924,7 +4930,7 @@
         <v>8045</v>
       </c>
       <c r="G39">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H39">
         <v>19</v>
@@ -4933,7 +4939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>124</v>
       </c>
@@ -4953,7 +4959,7 @@
         <v>545</v>
       </c>
       <c r="G40">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H40">
         <v>9</v>
@@ -4962,7 +4968,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>127</v>
       </c>
@@ -4982,7 +4988,7 @@
         <v>1375</v>
       </c>
       <c r="G41">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H41">
         <v>15</v>
@@ -4991,7 +4997,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>130</v>
       </c>
@@ -5011,7 +5017,7 @@
         <v>2945</v>
       </c>
       <c r="G42">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H42">
         <v>9</v>
@@ -5020,7 +5026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>133</v>
       </c>
@@ -5040,7 +5046,7 @@
         <v>5010</v>
       </c>
       <c r="G43">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H43">
         <v>12</v>
@@ -5049,7 +5055,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>136</v>
       </c>
@@ -5069,7 +5075,7 @@
         <v>5640</v>
       </c>
       <c r="G44">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H44">
         <v>6</v>
@@ -5078,7 +5084,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>139</v>
       </c>
@@ -5098,7 +5104,7 @@
         <v>5980</v>
       </c>
       <c r="G45">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H45">
         <v>10</v>
@@ -5107,7 +5113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>142</v>
       </c>
@@ -5127,7 +5133,7 @@
         <v>4095</v>
       </c>
       <c r="G46">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H46">
         <v>6</v>
@@ -5136,7 +5142,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>145</v>
       </c>
@@ -5156,7 +5162,7 @@
         <v>8500</v>
       </c>
       <c r="G47">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H47">
         <v>17</v>
@@ -5165,7 +5171,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -5185,7 +5191,7 @@
         <v>1865</v>
       </c>
       <c r="G48">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <v>5</v>
@@ -5194,7 +5200,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>151</v>
       </c>
@@ -5214,7 +5220,7 @@
         <v>4380</v>
       </c>
       <c r="G49">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <v>10</v>
@@ -5223,7 +5229,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>154</v>
       </c>
@@ -5243,7 +5249,7 @@
         <v>7535</v>
       </c>
       <c r="G50">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H50">
         <v>19</v>
@@ -5252,7 +5258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>157</v>
       </c>
@@ -5272,7 +5278,7 @@
         <v>5215</v>
       </c>
       <c r="G51">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H51">
         <v>16</v>
@@ -5281,7 +5287,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>160</v>
       </c>
@@ -5301,7 +5307,7 @@
         <v>3255</v>
       </c>
       <c r="G52">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H52">
         <v>7</v>
@@ -5310,7 +5316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -5330,7 +5336,7 @@
         <v>2610</v>
       </c>
       <c r="G53">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H53">
         <v>19</v>
@@ -5339,7 +5345,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>166</v>
       </c>
@@ -5359,7 +5365,7 @@
         <v>4765</v>
       </c>
       <c r="G54">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H54">
         <v>9</v>
@@ -5368,7 +5374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>169</v>
       </c>
@@ -5388,7 +5394,7 @@
         <v>7140</v>
       </c>
       <c r="G55">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H55">
         <v>9</v>
@@ -5397,7 +5403,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>172</v>
       </c>
@@ -5417,7 +5423,7 @@
         <v>3395</v>
       </c>
       <c r="G56">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H56">
         <v>5</v>
@@ -5426,7 +5432,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>175</v>
       </c>
@@ -5446,7 +5452,7 @@
         <v>2810</v>
       </c>
       <c r="G57">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H57">
         <v>11</v>
@@ -5455,7 +5461,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>178</v>
       </c>
@@ -5475,7 +5481,7 @@
         <v>3915</v>
       </c>
       <c r="G58">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H58">
         <v>11</v>
@@ -5484,7 +5490,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>181</v>
       </c>
@@ -5504,7 +5510,7 @@
         <v>5020</v>
       </c>
       <c r="G59">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H59">
         <v>17</v>
@@ -5513,7 +5519,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>184</v>
       </c>
@@ -5533,7 +5539,7 @@
         <v>6050</v>
       </c>
       <c r="G60">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H60">
         <v>8</v>
@@ -5542,7 +5548,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>187</v>
       </c>
@@ -5562,7 +5568,7 @@
         <v>3830</v>
       </c>
       <c r="G61">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>16</v>
@@ -5571,7 +5577,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>190</v>
       </c>
@@ -5591,7 +5597,7 @@
         <v>3580</v>
       </c>
       <c r="G62">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H62">
         <v>11</v>
@@ -5600,7 +5606,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>193</v>
       </c>
@@ -5620,7 +5626,7 @@
         <v>4050</v>
       </c>
       <c r="G63">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H63">
         <v>6</v>
@@ -5629,7 +5635,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>196</v>
       </c>
@@ -5649,7 +5655,7 @@
         <v>4090</v>
       </c>
       <c r="G64">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>15</v>
@@ -5658,7 +5664,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>199</v>
       </c>
@@ -5678,7 +5684,7 @@
         <v>3150</v>
       </c>
       <c r="G65">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H65">
         <v>15</v>
@@ -5687,7 +5693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>202</v>
       </c>
@@ -5707,7 +5713,7 @@
         <v>6995</v>
       </c>
       <c r="G66">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H66">
         <v>15</v>
@@ -5716,7 +5722,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>205</v>
       </c>
@@ -5736,7 +5742,7 @@
         <v>4635</v>
       </c>
       <c r="G67">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H67">
         <v>10</v>
@@ -5745,7 +5751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>208</v>
       </c>
@@ -5765,7 +5771,7 @@
         <v>4085</v>
       </c>
       <c r="G68">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>10</v>
@@ -5774,7 +5780,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>211</v>
       </c>
@@ -5794,7 +5800,7 @@
         <v>5765</v>
       </c>
       <c r="G69">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H69">
         <v>6</v>
@@ -5803,7 +5809,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>214</v>
       </c>
@@ -5823,7 +5829,7 @@
         <v>5230</v>
       </c>
       <c r="G70">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>16</v>
@@ -5832,7 +5838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>217</v>
       </c>
@@ -5852,7 +5858,7 @@
         <v>925</v>
       </c>
       <c r="G71">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H71">
         <v>5</v>
@@ -5861,7 +5867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>220</v>
       </c>
@@ -5881,7 +5887,7 @@
         <v>3485</v>
       </c>
       <c r="G72">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <v>9</v>
@@ -5890,7 +5896,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>223</v>
       </c>
@@ -5910,7 +5916,7 @@
         <v>5320</v>
       </c>
       <c r="G73">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>7</v>
@@ -5919,7 +5925,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>226</v>
       </c>
@@ -5939,7 +5945,7 @@
         <v>330</v>
       </c>
       <c r="G74">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H74">
         <v>19</v>
@@ -5948,7 +5954,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>229</v>
       </c>
@@ -5968,7 +5974,7 @@
         <v>7745</v>
       </c>
       <c r="G75">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H75">
         <v>19</v>
@@ -5977,7 +5983,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>232</v>
       </c>
@@ -5997,7 +6003,7 @@
         <v>6545</v>
       </c>
       <c r="G76">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H76">
         <v>8</v>
@@ -6006,7 +6012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>235</v>
       </c>
@@ -6026,7 +6032,7 @@
         <v>4905</v>
       </c>
       <c r="G77">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H77">
         <v>10</v>
@@ -6035,7 +6041,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>238</v>
       </c>
@@ -6055,7 +6061,7 @@
         <v>45385</v>
       </c>
       <c r="G78">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H78">
         <v>18</v>
@@ -6064,7 +6070,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>242</v>
       </c>
@@ -6084,7 +6090,7 @@
         <v>33890</v>
       </c>
       <c r="G79">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H79">
         <v>7</v>
@@ -6093,7 +6099,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>245</v>
       </c>
@@ -6113,7 +6119,7 @@
         <v>38595</v>
       </c>
       <c r="G80">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H80">
         <v>15</v>
@@ -6122,7 +6128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>248</v>
       </c>
@@ -6142,7 +6148,7 @@
         <v>9010</v>
       </c>
       <c r="G81">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H81">
         <v>19</v>
@@ -6151,7 +6157,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>251</v>
       </c>
@@ -6171,7 +6177,7 @@
         <v>23780</v>
       </c>
       <c r="G82">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <v>11</v>
@@ -6180,7 +6186,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>254</v>
       </c>
@@ -6200,7 +6206,7 @@
         <v>36020</v>
       </c>
       <c r="G83">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H83">
         <v>9</v>
@@ -6209,7 +6215,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>257</v>
       </c>
@@ -6229,7 +6235,7 @@
         <v>34685</v>
       </c>
       <c r="G84">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H84">
         <v>10</v>
@@ -6238,7 +6244,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>260</v>
       </c>
@@ -6258,7 +6264,7 @@
         <v>19735</v>
       </c>
       <c r="G85">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H85">
         <v>5</v>
@@ -6267,7 +6273,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>263</v>
       </c>
@@ -6287,7 +6293,7 @@
         <v>18745</v>
       </c>
       <c r="G86">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <v>11</v>
@@ -6296,7 +6302,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>266</v>
       </c>
@@ -6316,7 +6322,7 @@
         <v>15260</v>
       </c>
       <c r="G87">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H87">
         <v>18</v>
@@ -6325,7 +6331,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>269</v>
       </c>
@@ -6345,7 +6351,7 @@
         <v>36495</v>
       </c>
       <c r="G88">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>10</v>
@@ -6354,7 +6360,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>272</v>
       </c>
@@ -6374,7 +6380,7 @@
         <v>7335</v>
       </c>
       <c r="G89">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H89">
         <v>10</v>
@@ -6383,7 +6389,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>275</v>
       </c>
@@ -6403,7 +6409,7 @@
         <v>47700</v>
       </c>
       <c r="G90">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H90">
         <v>12</v>
@@ -6412,7 +6418,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>278</v>
       </c>
@@ -6432,7 +6438,7 @@
         <v>37680</v>
       </c>
       <c r="G91">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H91">
         <v>6</v>
@@ -6441,7 +6447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>281</v>
       </c>
@@ -6461,7 +6467,7 @@
         <v>35895</v>
       </c>
       <c r="G92">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>17</v>
@@ -6470,7 +6476,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>284</v>
       </c>
@@ -6490,7 +6496,7 @@
         <v>16045</v>
       </c>
       <c r="G93">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H93">
         <v>15</v>
@@ -6499,7 +6505,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>287</v>
       </c>
@@ -6519,7 +6525,7 @@
         <v>4470</v>
       </c>
       <c r="G94">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H94">
         <v>9</v>
@@ -6528,7 +6534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>290</v>
       </c>
@@ -6548,7 +6554,7 @@
         <v>7245</v>
       </c>
       <c r="G95">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <v>15</v>
@@ -6557,7 +6563,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>293</v>
       </c>
@@ -6577,7 +6583,7 @@
         <v>30135</v>
       </c>
       <c r="G96">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H96">
         <v>18</v>
@@ -6586,7 +6592,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>296</v>
       </c>
@@ -6606,7 +6612,7 @@
         <v>44810</v>
       </c>
       <c r="G97">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>9</v>
@@ -6615,7 +6621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>299</v>
       </c>
@@ -6635,7 +6641,7 @@
         <v>24155</v>
       </c>
       <c r="G98">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H98">
         <v>5</v>
@@ -6644,7 +6650,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>302</v>
       </c>
@@ -6664,7 +6670,7 @@
         <v>28620</v>
       </c>
       <c r="G99">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <v>11</v>
@@ -6673,7 +6679,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>305</v>
       </c>
@@ -6693,7 +6699,7 @@
         <v>4090</v>
       </c>
       <c r="G100">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H100">
         <v>18</v>
@@ -6702,7 +6708,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>308</v>
       </c>
@@ -6722,7 +6728,7 @@
         <v>13895</v>
       </c>
       <c r="G101">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H101">
         <v>17</v>
@@ -6731,7 +6737,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>311</v>
       </c>
@@ -6751,7 +6757,7 @@
         <v>30250</v>
       </c>
       <c r="G102">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H102">
         <v>18</v>
@@ -6760,7 +6766,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>314</v>
       </c>
@@ -6780,7 +6786,7 @@
         <v>14235</v>
       </c>
       <c r="G103">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>7</v>
@@ -6789,7 +6795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>317</v>
       </c>
@@ -6809,7 +6815,7 @@
         <v>41240</v>
       </c>
       <c r="G104">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H104">
         <v>12</v>
@@ -6818,7 +6824,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>320</v>
       </c>
@@ -6838,7 +6844,7 @@
         <v>20120</v>
       </c>
       <c r="G105">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H105">
         <v>7</v>
@@ -6847,7 +6853,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>323</v>
       </c>
@@ -6867,7 +6873,7 @@
         <v>24015</v>
       </c>
       <c r="G106">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H106">
         <v>10</v>
@@ -6876,7 +6882,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>326</v>
       </c>
@@ -6896,7 +6902,7 @@
         <v>40290</v>
       </c>
       <c r="G107">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H107">
         <v>18</v>
@@ -6905,7 +6911,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>329</v>
       </c>
@@ -6925,7 +6931,7 @@
         <v>24030</v>
       </c>
       <c r="G108">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>16</v>
@@ -6934,7 +6940,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>332</v>
       </c>
@@ -6954,7 +6960,7 @@
         <v>35500</v>
       </c>
       <c r="G109">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H109">
         <v>15</v>
@@ -6963,7 +6969,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>335</v>
       </c>
@@ -6983,7 +6989,7 @@
         <v>17275</v>
       </c>
       <c r="G110">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H110">
         <v>19</v>
@@ -6992,7 +6998,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>338</v>
       </c>
@@ -7012,7 +7018,7 @@
         <v>10420</v>
       </c>
       <c r="G111">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H111">
         <v>19</v>
@@ -7021,7 +7027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>341</v>
       </c>
@@ -7041,7 +7047,7 @@
         <v>40205</v>
       </c>
       <c r="G112">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H112">
         <v>8</v>
@@ -7050,7 +7056,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>344</v>
       </c>
@@ -7070,7 +7076,7 @@
         <v>21125</v>
       </c>
       <c r="G113">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H113">
         <v>12</v>
@@ -7079,7 +7085,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>347</v>
       </c>
@@ -7099,7 +7105,7 @@
         <v>45290</v>
       </c>
       <c r="G114">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H114">
         <v>9</v>
@@ -7108,7 +7114,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>350</v>
       </c>
@@ -7128,7 +7134,7 @@
         <v>7860</v>
       </c>
       <c r="G115">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H115">
         <v>8</v>
@@ -7137,7 +7143,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>353</v>
       </c>
@@ -7157,7 +7163,7 @@
         <v>16525</v>
       </c>
       <c r="G116">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H116">
         <v>12</v>
@@ -7166,7 +7172,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>356</v>
       </c>
@@ -7186,7 +7192,7 @@
         <v>17235</v>
       </c>
       <c r="G117">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H117">
         <v>14</v>
@@ -7195,7 +7201,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>359</v>
       </c>
@@ -7215,7 +7221,7 @@
         <v>16585</v>
       </c>
       <c r="G118">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H118">
         <v>14</v>
@@ -7224,7 +7230,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>362</v>
       </c>
@@ -7244,7 +7250,7 @@
         <v>19835</v>
       </c>
       <c r="G119">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H119">
         <v>16</v>
@@ -7253,7 +7259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>365</v>
       </c>
@@ -7273,7 +7279,7 @@
         <v>19505</v>
       </c>
       <c r="G120">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H120">
         <v>18</v>
@@ -7282,7 +7288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>368</v>
       </c>
@@ -7302,7 +7308,7 @@
         <v>19265</v>
       </c>
       <c r="G121">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H121">
         <v>14</v>
@@ -7311,7 +7317,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>372</v>
       </c>
@@ -7331,7 +7337,7 @@
         <v>2050</v>
       </c>
       <c r="G122">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H122">
         <v>13</v>
@@ -7340,7 +7346,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>375</v>
       </c>
@@ -7360,7 +7366,7 @@
         <v>8160</v>
       </c>
       <c r="G123">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H123">
         <v>15</v>
@@ -7369,7 +7375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>378</v>
       </c>
@@ -7389,7 +7395,7 @@
         <v>19945</v>
       </c>
       <c r="G124">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H124">
         <v>9</v>
@@ -7398,7 +7404,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>381</v>
       </c>
@@ -7418,7 +7424,7 @@
         <v>2850</v>
       </c>
       <c r="G125">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H125">
         <v>18</v>
@@ -7427,7 +7433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>384</v>
       </c>
@@ -7447,7 +7453,7 @@
         <v>15955</v>
       </c>
       <c r="G126">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H126">
         <v>9</v>
@@ -7456,7 +7462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>387</v>
       </c>
@@ -7476,7 +7482,7 @@
         <v>10600</v>
       </c>
       <c r="G127">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H127">
         <v>15</v>
@@ -7485,7 +7491,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>390</v>
       </c>
@@ -7505,7 +7511,7 @@
         <v>23080</v>
       </c>
       <c r="G128">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H128">
         <v>12</v>
@@ -7514,7 +7520,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>393</v>
       </c>
@@ -7534,7 +7540,7 @@
         <v>8910</v>
       </c>
       <c r="G129">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H129">
         <v>15</v>
@@ -7543,7 +7549,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>396</v>
       </c>
@@ -7563,7 +7569,7 @@
         <v>21310</v>
       </c>
       <c r="G130">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H130">
         <v>7</v>
@@ -7572,7 +7578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>399</v>
       </c>
@@ -7592,7 +7598,7 @@
         <v>12175</v>
       </c>
       <c r="G131">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H131">
         <v>10</v>
@@ -7601,7 +7607,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>402</v>
       </c>
@@ -7621,7 +7627,7 @@
         <v>25115</v>
       </c>
       <c r="G132">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H132">
         <v>16</v>
@@ -7630,7 +7636,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>405</v>
       </c>
@@ -7650,7 +7656,7 @@
         <v>7975</v>
       </c>
       <c r="G133">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H133">
         <v>16</v>
@@ -7659,7 +7665,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>408</v>
       </c>
@@ -7679,7 +7685,7 @@
         <v>12795</v>
       </c>
       <c r="G134">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H134">
         <v>18</v>
@@ -7688,7 +7694,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>411</v>
       </c>
@@ -7708,7 +7714,7 @@
         <v>17345</v>
       </c>
       <c r="G135">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H135">
         <v>10</v>
@@ -7717,7 +7723,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>414</v>
       </c>
@@ -7737,7 +7743,7 @@
         <v>25420</v>
       </c>
       <c r="G136">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H136">
         <v>9</v>
@@ -7746,7 +7752,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>417</v>
       </c>
@@ -7766,7 +7772,7 @@
         <v>18550</v>
       </c>
       <c r="G137">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H137">
         <v>13</v>
@@ -7775,7 +7781,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>420</v>
       </c>
@@ -7795,7 +7801,7 @@
         <v>740</v>
       </c>
       <c r="G138">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H138">
         <v>6</v>
@@ -7804,7 +7810,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>423</v>
       </c>
@@ -7824,7 +7830,7 @@
         <v>2225</v>
       </c>
       <c r="G139">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H139">
         <v>15</v>
@@ -7833,7 +7839,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>426</v>
       </c>
@@ -7853,7 +7859,7 @@
         <v>3235</v>
       </c>
       <c r="G140">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H140">
         <v>18</v>
@@ -7862,7 +7868,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>429</v>
       </c>
@@ -7882,7 +7888,7 @@
         <v>16055</v>
       </c>
       <c r="G141">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H141">
         <v>5</v>
@@ -7891,7 +7897,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>432</v>
       </c>
@@ -7911,7 +7917,7 @@
         <v>23560</v>
       </c>
       <c r="G142">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H142">
         <v>11</v>
@@ -7920,7 +7926,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>435</v>
       </c>
@@ -7940,7 +7946,7 @@
         <v>5255</v>
       </c>
       <c r="G143">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H143">
         <v>14</v>
@@ -7949,7 +7955,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>438</v>
       </c>
@@ -7969,7 +7975,7 @@
         <v>11205</v>
       </c>
       <c r="G144">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H144">
         <v>12</v>
@@ -7978,7 +7984,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>441</v>
       </c>
@@ -7998,7 +8004,7 @@
         <v>25815</v>
       </c>
       <c r="G145">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H145">
         <v>18</v>
@@ -8007,7 +8013,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>444</v>
       </c>
@@ -8027,7 +8033,7 @@
         <v>2935</v>
       </c>
       <c r="G146">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H146">
         <v>10</v>
@@ -8036,7 +8042,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>447</v>
       </c>
@@ -8056,7 +8062,7 @@
         <v>10085</v>
       </c>
       <c r="G147">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H147">
         <v>11</v>
@@ -8065,7 +8071,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>450</v>
       </c>
@@ -8085,7 +8091,7 @@
         <v>15205</v>
       </c>
       <c r="G148">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H148">
         <v>16</v>
@@ -8094,7 +8100,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>453</v>
       </c>
@@ -8114,7 +8120,7 @@
         <v>2220</v>
       </c>
       <c r="G149">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H149">
         <v>17</v>
@@ -8123,7 +8129,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>456</v>
       </c>
@@ -8143,7 +8149,7 @@
         <v>20555</v>
       </c>
       <c r="G150">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H150">
         <v>6</v>
@@ -8152,7 +8158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>459</v>
       </c>
@@ -8172,7 +8178,7 @@
         <v>8230</v>
       </c>
       <c r="G151">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H151">
         <v>6</v>
@@ -8181,7 +8187,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>462</v>
       </c>
@@ -8201,7 +8207,7 @@
         <v>18880</v>
       </c>
       <c r="G152">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H152">
         <v>16</v>
@@ -8210,7 +8216,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>465</v>
       </c>
@@ -8230,7 +8236,7 @@
         <v>10805</v>
       </c>
       <c r="G153">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H153">
         <v>7</v>
@@ -8239,7 +8245,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>468</v>
       </c>
@@ -8259,7 +8265,7 @@
         <v>1745</v>
       </c>
       <c r="G154">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H154">
         <v>15</v>
@@ -8268,7 +8274,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>471</v>
       </c>
@@ -8288,7 +8294,7 @@
         <v>8210</v>
       </c>
       <c r="G155">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H155">
         <v>10</v>
@@ -8297,7 +8303,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>474</v>
       </c>
@@ -8317,7 +8323,7 @@
         <v>16385</v>
       </c>
       <c r="G156">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H156">
         <v>5</v>
@@ -8326,7 +8332,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>477</v>
       </c>
@@ -8346,7 +8352,7 @@
         <v>23160</v>
       </c>
       <c r="G157">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H157">
         <v>9</v>
@@ -8355,7 +8361,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>480</v>
       </c>
@@ -8375,7 +8381,7 @@
         <v>8145</v>
       </c>
       <c r="G158">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H158">
         <v>8</v>
@@ -8384,7 +8390,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>483</v>
       </c>
@@ -8404,7 +8410,7 @@
         <v>23865</v>
       </c>
       <c r="G159">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H159">
         <v>14</v>
@@ -8413,7 +8419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>486</v>
       </c>
@@ -8433,7 +8439,7 @@
         <v>21550</v>
       </c>
       <c r="G160">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H160">
         <v>15</v>
@@ -8442,7 +8448,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>489</v>
       </c>
@@ -8462,7 +8468,7 @@
         <v>9985</v>
       </c>
       <c r="G161">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H161">
         <v>9</v>
@@ -8471,7 +8477,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>492</v>
       </c>
@@ -8491,7 +8497,7 @@
         <v>27010</v>
       </c>
       <c r="G162">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H162">
         <v>6</v>
@@ -8500,7 +8506,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>495</v>
       </c>
@@ -8520,7 +8526,7 @@
         <v>11165</v>
       </c>
       <c r="G163">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H163">
         <v>16</v>
@@ -8529,7 +8535,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>499</v>
       </c>
@@ -8549,7 +8555,7 @@
         <v>4015</v>
       </c>
       <c r="G164">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H164">
         <v>7</v>
@@ -8558,7 +8564,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>502</v>
       </c>
@@ -8578,7 +8584,7 @@
         <v>11220</v>
       </c>
       <c r="G165">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H165">
         <v>6</v>
@@ -8587,7 +8593,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>505</v>
       </c>
@@ -8607,7 +8613,7 @@
         <v>4235</v>
       </c>
       <c r="G166">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H166">
         <v>8</v>
@@ -8616,7 +8622,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>508</v>
       </c>
@@ -8636,7 +8642,7 @@
         <v>9070</v>
       </c>
       <c r="G167">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H167">
         <v>10</v>
@@ -8645,7 +8651,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>511</v>
       </c>
@@ -8665,7 +8671,7 @@
         <v>2405</v>
       </c>
       <c r="G168">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H168">
         <v>6</v>
@@ -8674,7 +8680,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>514</v>
       </c>
@@ -8694,7 +8700,7 @@
         <v>10480</v>
       </c>
       <c r="G169">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H169">
         <v>5</v>
@@ -8703,7 +8709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>517</v>
       </c>
@@ -8723,7 +8729,7 @@
         <v>5200</v>
       </c>
       <c r="G170">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H170">
         <v>11</v>
@@ -8732,7 +8738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>520</v>
       </c>
@@ -8752,7 +8758,7 @@
         <v>10020</v>
       </c>
       <c r="G171">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H171">
         <v>7</v>
@@ -8761,7 +8767,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>523</v>
       </c>
@@ -8781,7 +8787,7 @@
         <v>3630</v>
       </c>
       <c r="G172">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H172">
         <v>19</v>
@@ -8790,7 +8796,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>526</v>
       </c>
@@ -8810,7 +8816,7 @@
         <v>4735</v>
       </c>
       <c r="G173">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H173">
         <v>15</v>
@@ -8819,7 +8825,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>529</v>
       </c>
@@ -8839,7 +8845,7 @@
         <v>6320</v>
       </c>
       <c r="G174">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H174">
         <v>11</v>
@@ -8848,7 +8854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>532</v>
       </c>
@@ -8868,7 +8874,7 @@
         <v>10360</v>
       </c>
       <c r="G175">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H175">
         <v>5</v>
@@ -8877,7 +8883,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>535</v>
       </c>
@@ -8897,7 +8903,7 @@
         <v>2495</v>
       </c>
       <c r="G176">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H176">
         <v>9</v>
@@ -8906,7 +8912,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>538</v>
       </c>
@@ -8926,7 +8932,7 @@
         <v>8495</v>
       </c>
       <c r="G177">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H177">
         <v>13</v>
@@ -8935,7 +8941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>541</v>
       </c>
@@ -8955,7 +8961,7 @@
         <v>3465</v>
       </c>
       <c r="G178">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H178">
         <v>6</v>
@@ -8964,7 +8970,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>544</v>
       </c>
@@ -8984,7 +8990,7 @@
         <v>7275</v>
       </c>
       <c r="G179">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H179">
         <v>7</v>
@@ -8993,7 +8999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>547</v>
       </c>
@@ -9013,7 +9019,7 @@
         <v>920</v>
       </c>
       <c r="G180">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H180">
         <v>10</v>
@@ -9022,7 +9028,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>550</v>
       </c>
@@ -9042,7 +9048,7 @@
         <v>520</v>
       </c>
       <c r="G181">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H181">
         <v>8</v>
@@ -9051,7 +9057,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>553</v>
       </c>
@@ -9071,7 +9077,7 @@
         <v>8470</v>
       </c>
       <c r="G182">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H182">
         <v>5</v>
@@ -9080,7 +9086,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>556</v>
       </c>
@@ -9100,7 +9106,7 @@
         <v>1765</v>
       </c>
       <c r="G183">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H183">
         <v>18</v>
@@ -9109,7 +9115,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>559</v>
       </c>
@@ -9129,7 +9135,7 @@
         <v>8480</v>
       </c>
       <c r="G184">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H184">
         <v>18</v>
@@ -9138,7 +9144,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>562</v>
       </c>
@@ -9158,7 +9164,7 @@
         <v>9580</v>
       </c>
       <c r="G185">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H185">
         <v>11</v>
@@ -9167,7 +9173,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>565</v>
       </c>
@@ -9187,7 +9193,7 @@
         <v>4865</v>
       </c>
       <c r="G186">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H186">
         <v>5</v>
@@ -9196,7 +9202,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>568</v>
       </c>
@@ -9216,7 +9222,7 @@
         <v>8050</v>
       </c>
       <c r="G187">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H187">
         <v>6</v>
@@ -9225,7 +9231,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>571</v>
       </c>
@@ -9245,7 +9251,7 @@
         <v>5290</v>
       </c>
       <c r="G188">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H188">
         <v>8</v>
@@ -9254,7 +9260,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>574</v>
       </c>
@@ -9274,7 +9280,7 @@
         <v>6090</v>
       </c>
       <c r="G189">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H189">
         <v>8</v>
@@ -9283,7 +9289,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>577</v>
       </c>
@@ -9303,7 +9309,7 @@
         <v>5070</v>
       </c>
       <c r="G190">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H190">
         <v>11</v>
@@ -9312,7 +9318,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>580</v>
       </c>
@@ -9332,7 +9338,7 @@
         <v>95</v>
       </c>
       <c r="G191">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H191">
         <v>10</v>
@@ -9341,7 +9347,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>583</v>
       </c>
@@ -9361,7 +9367,7 @@
         <v>2785</v>
       </c>
       <c r="G192">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H192">
         <v>7</v>
@@ -9370,7 +9376,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>586</v>
       </c>
@@ -9390,7 +9396,7 @@
         <v>5490</v>
       </c>
       <c r="G193">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H193">
         <v>7</v>
@@ -9399,7 +9405,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>589</v>
       </c>
@@ -9419,7 +9425,7 @@
         <v>12325</v>
       </c>
       <c r="G194">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H194">
         <v>5</v>
@@ -9428,7 +9434,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>592</v>
       </c>
@@ -9448,7 +9454,7 @@
         <v>8640</v>
       </c>
       <c r="G195">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H195">
         <v>14</v>
@@ -9457,7 +9463,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>595</v>
       </c>
@@ -9477,7 +9483,7 @@
         <v>9670</v>
       </c>
       <c r="G196">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H196">
         <v>9</v>
@@ -9486,7 +9492,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>598</v>
       </c>
@@ -9506,7 +9512,7 @@
         <v>5315</v>
       </c>
       <c r="G197">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H197">
         <v>16</v>
@@ -9515,7 +9521,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>601</v>
       </c>
@@ -9535,7 +9541,7 @@
         <v>4470</v>
       </c>
       <c r="G198">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H198">
         <v>19</v>
@@ -9544,7 +9550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>604</v>
       </c>
@@ -9564,7 +9570,7 @@
         <v>7135</v>
       </c>
       <c r="G199">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H199">
         <v>18</v>
@@ -9573,7 +9579,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>607</v>
       </c>
@@ -9593,7 +9599,7 @@
         <v>11530</v>
       </c>
       <c r="G200">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H200">
         <v>15</v>
@@ -9602,7 +9608,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>610</v>
       </c>
@@ -9622,7 +9628,7 @@
         <v>6185</v>
       </c>
       <c r="G201">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H201">
         <v>8</v>
@@ -9631,7 +9637,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>613</v>
       </c>
@@ -9651,7 +9657,7 @@
         <v>10085</v>
       </c>
       <c r="G202">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H202">
         <v>15</v>
@@ -9660,7 +9666,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>616</v>
       </c>
@@ -9680,7 +9686,7 @@
         <v>9520</v>
       </c>
       <c r="G203">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H203">
         <v>17</v>
@@ -9689,7 +9695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>620</v>
       </c>
@@ -9709,7 +9715,7 @@
         <v>5125</v>
       </c>
       <c r="G204">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H204">
         <v>6</v>
@@ -9718,7 +9724,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>623</v>
       </c>
@@ -9738,7 +9744,7 @@
         <v>4465</v>
       </c>
       <c r="G205">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H205">
         <v>9</v>
@@ -9747,7 +9753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>626</v>
       </c>
@@ -9767,7 +9773,7 @@
         <v>4420</v>
       </c>
       <c r="G206">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H206">
         <v>18</v>
@@ -9776,7 +9782,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>629</v>
       </c>
@@ -9796,7 +9802,7 @@
         <v>2485</v>
       </c>
       <c r="G207">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H207">
         <v>19</v>
@@ -9805,7 +9811,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>632</v>
       </c>
@@ -9825,7 +9831,7 @@
         <v>12135</v>
       </c>
       <c r="G208">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H208">
         <v>6</v>
@@ -9834,7 +9840,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>635</v>
       </c>
@@ -9854,7 +9860,7 @@
         <v>1850</v>
       </c>
       <c r="G209">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H209">
         <v>16</v>
@@ -9863,7 +9869,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>638</v>
       </c>
@@ -9883,7 +9889,7 @@
         <v>8920</v>
       </c>
       <c r="G210">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H210">
         <v>5</v>
@@ -9892,7 +9898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>641</v>
       </c>
@@ -9912,7 +9918,7 @@
         <v>10735</v>
       </c>
       <c r="G211">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H211">
         <v>15</v>
@@ -9921,7 +9927,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>644</v>
       </c>
@@ -9941,7 +9947,7 @@
         <v>1370</v>
       </c>
       <c r="G212">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H212">
         <v>16</v>
@@ -9950,7 +9956,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>647</v>
       </c>
@@ -9970,7 +9976,7 @@
         <v>5035</v>
       </c>
       <c r="G213">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H213">
         <v>9</v>
@@ -9979,7 +9985,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>650</v>
       </c>
@@ -9999,7 +10005,7 @@
         <v>6565</v>
       </c>
       <c r="G214">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H214">
         <v>13</v>
@@ -10008,7 +10014,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>653</v>
       </c>
@@ -10028,7 +10034,7 @@
         <v>4020</v>
       </c>
       <c r="G215">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H215">
         <v>10</v>
@@ -10037,7 +10043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>656</v>
       </c>
@@ -10057,7 +10063,7 @@
         <v>8135</v>
       </c>
       <c r="G216">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H216">
         <v>17</v>
@@ -10066,7 +10072,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>659</v>
       </c>
@@ -10086,7 +10092,7 @@
         <v>5835</v>
       </c>
       <c r="G217">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H217">
         <v>11</v>
@@ -10095,7 +10101,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>662</v>
       </c>
@@ -10115,7 +10121,7 @@
         <v>945</v>
       </c>
       <c r="G218">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H218">
         <v>19</v>
@@ -10124,7 +10130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>665</v>
       </c>
@@ -10144,7 +10150,7 @@
         <v>11730</v>
       </c>
       <c r="G219">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H219">
         <v>18</v>
@@ -10153,7 +10159,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>668</v>
       </c>
@@ -10173,7 +10179,7 @@
         <v>7765</v>
       </c>
       <c r="G220">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H220">
         <v>9</v>
@@ -10182,7 +10188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>671</v>
       </c>
@@ -10202,7 +10208,7 @@
         <v>5290</v>
       </c>
       <c r="G221">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H221">
         <v>9</v>
@@ -10211,7 +10217,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>674</v>
       </c>
@@ -10231,7 +10237,7 @@
         <v>8760</v>
       </c>
       <c r="G222">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H222">
         <v>5</v>
@@ -10240,7 +10246,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>677</v>
       </c>
@@ -10260,7 +10266,7 @@
         <v>11325</v>
       </c>
       <c r="G223">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H223">
         <v>15</v>
@@ -10269,7 +10275,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>680</v>
       </c>
@@ -10289,7 +10295,7 @@
         <v>8655</v>
       </c>
       <c r="G224">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H224">
         <v>18</v>
@@ -10298,7 +10304,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>683</v>
       </c>
@@ -10318,7 +10324,7 @@
         <v>6080</v>
       </c>
       <c r="G225">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H225">
         <v>14</v>
@@ -10327,7 +10333,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>686</v>
       </c>
@@ -10347,7 +10353,7 @@
         <v>8560</v>
       </c>
       <c r="G226">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H226">
         <v>8</v>
@@ -10356,7 +10362,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>689</v>
       </c>
@@ -10376,7 +10382,7 @@
         <v>3775</v>
       </c>
       <c r="G227">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H227">
         <v>8</v>
@@ -10385,7 +10391,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>692</v>
       </c>
@@ -10405,7 +10411,7 @@
         <v>1730</v>
       </c>
       <c r="G228">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H228">
         <v>11</v>
@@ -10414,7 +10420,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>695</v>
       </c>
@@ -10434,7 +10440,7 @@
         <v>10390</v>
       </c>
       <c r="G229">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H229">
         <v>6</v>
@@ -10443,7 +10449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>698</v>
       </c>
@@ -10463,7 +10469,7 @@
         <v>6125</v>
       </c>
       <c r="G230">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H230">
         <v>5</v>
@@ -10472,7 +10478,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>701</v>
       </c>
@@ -10492,7 +10498,7 @@
         <v>2100</v>
       </c>
       <c r="G231">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H231">
         <v>8</v>
@@ -10501,7 +10507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>704</v>
       </c>
@@ -10521,7 +10527,7 @@
         <v>5660</v>
       </c>
       <c r="G232">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H232">
         <v>7</v>
@@ -10530,7 +10536,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>707</v>
       </c>
@@ -10550,7 +10556,7 @@
         <v>3775</v>
       </c>
       <c r="G233">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H233">
         <v>12</v>
@@ -10559,7 +10565,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>710</v>
       </c>
@@ -10579,7 +10585,7 @@
         <v>270</v>
       </c>
       <c r="G234">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H234">
         <v>9</v>
@@ -10588,7 +10594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>714</v>
       </c>
@@ -10608,7 +10614,7 @@
         <v>1570</v>
       </c>
       <c r="G235">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H235">
         <v>14</v>
@@ -10617,7 +10623,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>717</v>
       </c>
@@ -10637,7 +10643,7 @@
         <v>455</v>
       </c>
       <c r="G236">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H236">
         <v>12</v>
@@ -10646,7 +10652,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>720</v>
       </c>
@@ -10666,7 +10672,7 @@
         <v>395</v>
       </c>
       <c r="G237">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H237">
         <v>5</v>
@@ -10675,7 +10681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>723</v>
       </c>
@@ -10695,7 +10701,7 @@
         <v>370</v>
       </c>
       <c r="G238">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H238">
         <v>19</v>
@@ -10704,7 +10710,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>726</v>
       </c>
@@ -10724,7 +10730,7 @@
         <v>1210</v>
       </c>
       <c r="G239">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H239">
         <v>11</v>
@@ -10733,7 +10739,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>729</v>
       </c>
@@ -10753,7 +10759,7 @@
         <v>560</v>
       </c>
       <c r="G240">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H240">
         <v>14</v>
@@ -10762,7 +10768,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>732</v>
       </c>
@@ -10782,7 +10788,7 @@
         <v>400</v>
       </c>
       <c r="G241">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H241">
         <v>19</v>
@@ -10791,7 +10797,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>735</v>
       </c>
@@ -10811,7 +10817,7 @@
         <v>905</v>
       </c>
       <c r="G242">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H242">
         <v>6</v>
@@ -10820,7 +10826,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>738</v>
       </c>
@@ -10840,7 +10846,7 @@
         <v>255</v>
       </c>
       <c r="G243">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H243">
         <v>10</v>
@@ -10849,7 +10855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>741</v>
       </c>
@@ -10869,7 +10875,7 @@
         <v>260</v>
       </c>
       <c r="G244">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H244">
         <v>15</v>
@@ -10878,7 +10884,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>744</v>
       </c>
@@ -10898,7 +10904,7 @@
         <v>1130</v>
       </c>
       <c r="G245">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H245">
         <v>15</v>
@@ -10907,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>747</v>
       </c>
@@ -10927,7 +10933,7 @@
         <v>545</v>
       </c>
       <c r="G246">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H246">
         <v>11</v>
@@ -10936,7 +10942,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>750</v>
       </c>
@@ -10956,7 +10962,7 @@
         <v>195</v>
       </c>
       <c r="G247">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H247">
         <v>15</v>
@@ -10965,7 +10971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>753</v>
       </c>
@@ -10985,7 +10991,7 @@
         <v>1085</v>
       </c>
       <c r="G248">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H248">
         <v>10</v>
@@ -10994,7 +11000,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>756</v>
       </c>
@@ -11014,7 +11020,7 @@
         <v>1025</v>
       </c>
       <c r="G249">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H249">
         <v>18</v>
@@ -11023,7 +11029,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>759</v>
       </c>
@@ -11043,7 +11049,7 @@
         <v>110</v>
       </c>
       <c r="G250">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H250">
         <v>16</v>
@@ -11052,7 +11058,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>762</v>
       </c>
@@ -11072,7 +11078,7 @@
         <v>1295</v>
       </c>
       <c r="G251">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H251">
         <v>6</v>
@@ -11081,7 +11087,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>765</v>
       </c>
@@ -11101,7 +11107,7 @@
         <v>1300</v>
       </c>
       <c r="G252">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H252">
         <v>19</v>
@@ -11110,7 +11116,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>768</v>
       </c>
@@ -11130,7 +11136,7 @@
         <v>1465</v>
       </c>
       <c r="G253">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H253">
         <v>15</v>
@@ -11139,7 +11145,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>771</v>
       </c>
@@ -11159,7 +11165,7 @@
         <v>880</v>
       </c>
       <c r="G254">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H254">
         <v>7</v>
@@ -11168,7 +11174,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>774</v>
       </c>
@@ -11188,7 +11194,7 @@
         <v>450</v>
       </c>
       <c r="G255">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H255">
         <v>14</v>
@@ -11197,7 +11203,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>777</v>
       </c>
@@ -11217,7 +11223,7 @@
         <v>645</v>
       </c>
       <c r="G256">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H256">
         <v>16</v>
@@ -11226,7 +11232,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>780</v>
       </c>
@@ -11246,7 +11252,7 @@
         <v>1030</v>
       </c>
       <c r="G257">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H257">
         <v>19</v>
@@ -11255,7 +11261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>783</v>
       </c>
@@ -11275,7 +11281,7 @@
         <v>455</v>
       </c>
       <c r="G258">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H258">
         <v>8</v>
@@ -11284,7 +11290,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>786</v>
       </c>
@@ -11304,7 +11310,7 @@
         <v>1055</v>
       </c>
       <c r="G259">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H259">
         <v>9</v>
@@ -11313,7 +11319,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>789</v>
       </c>
@@ -11333,7 +11339,7 @@
         <v>935</v>
       </c>
       <c r="G260">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H260">
         <v>9</v>
@@ -11342,7 +11348,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>792</v>
       </c>
@@ -11362,7 +11368,7 @@
         <v>1485</v>
       </c>
       <c r="G261">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H261">
         <v>13</v>
@@ -11371,7 +11377,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>795</v>
       </c>
@@ -11391,7 +11397,7 @@
         <v>720</v>
       </c>
       <c r="G262">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H262">
         <v>5</v>
@@ -11400,7 +11406,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>798</v>
       </c>
@@ -11420,7 +11426,7 @@
         <v>535</v>
       </c>
       <c r="G263">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H263">
         <v>14</v>
@@ -11429,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>801</v>
       </c>
@@ -11449,7 +11455,7 @@
         <v>500</v>
       </c>
       <c r="G264">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H264">
         <v>8</v>
@@ -11458,7 +11464,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>804</v>
       </c>
@@ -11478,7 +11484,7 @@
         <v>730</v>
       </c>
       <c r="G265">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H265">
         <v>7</v>
@@ -11487,7 +11493,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>807</v>
       </c>
@@ -11507,7 +11513,7 @@
         <v>1700</v>
       </c>
       <c r="G266">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H266">
         <v>19</v>
@@ -11516,7 +11522,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>810</v>
       </c>
@@ -11536,7 +11542,7 @@
         <v>310</v>
       </c>
       <c r="G267">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H267">
         <v>17</v>
@@ -11545,7 +11551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>813</v>
       </c>
@@ -11565,7 +11571,7 @@
         <v>120</v>
       </c>
       <c r="G268">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H268">
         <v>15</v>
@@ -11574,7 +11580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>816</v>
       </c>
@@ -11594,7 +11600,7 @@
         <v>1420</v>
       </c>
       <c r="G269">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H269">
         <v>18</v>
@@ -11603,7 +11609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>819</v>
       </c>
@@ -11623,7 +11629,7 @@
         <v>695</v>
       </c>
       <c r="G270">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H270">
         <v>13</v>
@@ -11632,7 +11638,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>822</v>
       </c>
@@ -11652,7 +11658,7 @@
         <v>1425</v>
       </c>
       <c r="G271">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H271">
         <v>12</v>
@@ -11661,7 +11667,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>825</v>
       </c>
@@ -11681,7 +11687,7 @@
         <v>400</v>
       </c>
       <c r="G272">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H272">
         <v>5</v>
@@ -11690,7 +11696,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>829</v>
       </c>
@@ -11710,7 +11716,7 @@
         <v>395</v>
       </c>
       <c r="G273">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H273">
         <v>9</v>
@@ -11719,7 +11725,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>832</v>
       </c>
@@ -11739,7 +11745,7 @@
         <v>190</v>
       </c>
       <c r="G274">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H274">
         <v>14</v>
@@ -11748,7 +11754,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>835</v>
       </c>
@@ -11768,7 +11774,7 @@
         <v>795</v>
       </c>
       <c r="G275">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H275">
         <v>5</v>
@@ -11777,7 +11783,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>838</v>
       </c>
@@ -11797,7 +11803,7 @@
         <v>330</v>
       </c>
       <c r="G276">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H276">
         <v>8</v>
@@ -11806,7 +11812,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>841</v>
       </c>
@@ -11826,7 +11832,7 @@
         <v>1215</v>
       </c>
       <c r="G277">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H277">
         <v>7</v>
@@ -11835,7 +11841,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>844</v>
       </c>
@@ -11855,7 +11861,7 @@
         <v>1085</v>
       </c>
       <c r="G278">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H278">
         <v>7</v>
@@ -11864,7 +11870,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>847</v>
       </c>
@@ -11884,7 +11890,7 @@
         <v>1270</v>
       </c>
       <c r="G279">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H279">
         <v>8</v>
@@ -11893,7 +11899,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>850</v>
       </c>
@@ -11913,7 +11919,7 @@
         <v>315</v>
       </c>
       <c r="G280">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H280">
         <v>12</v>
@@ -11922,7 +11928,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>853</v>
       </c>
@@ -11942,7 +11948,7 @@
         <v>300</v>
       </c>
       <c r="G281">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H281">
         <v>17</v>
@@ -11951,7 +11957,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>856</v>
       </c>
@@ -11971,7 +11977,7 @@
         <v>960</v>
       </c>
       <c r="G282">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H282">
         <v>8</v>
@@ -11980,7 +11986,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>859</v>
       </c>
@@ -12000,7 +12006,7 @@
         <v>350</v>
       </c>
       <c r="G283">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H283">
         <v>5</v>
@@ -12009,7 +12015,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>862</v>
       </c>
@@ -12029,7 +12035,7 @@
         <v>840</v>
       </c>
       <c r="G284">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H284">
         <v>14</v>
@@ -12038,7 +12044,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>865</v>
       </c>
@@ -12058,7 +12064,7 @@
         <v>1320</v>
       </c>
       <c r="G285">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H285">
         <v>18</v>
@@ -12067,7 +12073,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>868</v>
       </c>
@@ -12087,7 +12093,7 @@
         <v>785</v>
       </c>
       <c r="G286">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H286">
         <v>13</v>
@@ -12096,7 +12102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>871</v>
       </c>
@@ -12116,7 +12122,7 @@
         <v>305</v>
       </c>
       <c r="G287">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H287">
         <v>8</v>
@@ -12125,7 +12131,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>874</v>
       </c>
@@ -12145,7 +12151,7 @@
         <v>500</v>
       </c>
       <c r="G288">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H288">
         <v>9</v>
@@ -12154,7 +12160,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>877</v>
       </c>
@@ -12174,7 +12180,7 @@
         <v>615</v>
       </c>
       <c r="G289">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H289">
         <v>14</v>
@@ -12183,7 +12189,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>880</v>
       </c>
@@ -12203,7 +12209,7 @@
         <v>1030</v>
       </c>
       <c r="G290">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H290">
         <v>5</v>
@@ -12212,7 +12218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>883</v>
       </c>
@@ -12232,7 +12238,7 @@
         <v>580</v>
       </c>
       <c r="G291">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H291">
         <v>13</v>
@@ -12241,7 +12247,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>886</v>
       </c>
@@ -12261,7 +12267,7 @@
         <v>1225</v>
       </c>
       <c r="G292">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H292">
         <v>16</v>
@@ -12270,7 +12276,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>889</v>
       </c>
@@ -12290,7 +12296,7 @@
         <v>940</v>
       </c>
       <c r="G293">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H293">
         <v>15</v>
@@ -12299,7 +12305,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>892</v>
       </c>
@@ -12319,7 +12325,7 @@
         <v>190</v>
       </c>
       <c r="G294">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H294">
         <v>14</v>
@@ -12328,7 +12334,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>895</v>
       </c>
@@ -12348,7 +12354,7 @@
         <v>625</v>
       </c>
       <c r="G295">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H295">
         <v>11</v>
@@ -12357,7 +12363,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>898</v>
       </c>
@@ -12377,7 +12383,7 @@
         <v>985</v>
       </c>
       <c r="G296">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H296">
         <v>6</v>
@@ -12386,7 +12392,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>901</v>
       </c>
@@ -12406,7 +12412,7 @@
         <v>1090</v>
       </c>
       <c r="G297">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H297">
         <v>7</v>
@@ -12415,7 +12421,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>904</v>
       </c>
@@ -12435,7 +12441,7 @@
         <v>875</v>
       </c>
       <c r="G298">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H298">
         <v>17</v>
@@ -12444,7 +12450,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>907</v>
       </c>
@@ -12464,7 +12470,7 @@
         <v>475</v>
       </c>
       <c r="G299">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H299">
         <v>13</v>
@@ -12473,7 +12479,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>910</v>
       </c>
@@ -12493,7 +12499,7 @@
         <v>400</v>
       </c>
       <c r="G300">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H300">
         <v>19</v>
@@ -12502,7 +12508,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>913</v>
       </c>
@@ -12522,7 +12528,7 @@
         <v>995</v>
       </c>
       <c r="G301">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H301">
         <v>19</v>
@@ -12531,7 +12537,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>916</v>
       </c>
@@ -12551,7 +12557,7 @@
         <v>4520</v>
       </c>
       <c r="G302">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H302">
         <v>15</v>
@@ -12560,7 +12566,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>920</v>
       </c>
@@ -12580,7 +12586,7 @@
         <v>5260</v>
       </c>
       <c r="G303">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H303">
         <v>16</v>
@@ -12589,7 +12595,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>923</v>
       </c>
@@ -12609,7 +12615,7 @@
         <v>5335</v>
       </c>
       <c r="G304">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H304">
         <v>16</v>
@@ -12618,7 +12624,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>926</v>
       </c>
@@ -12638,7 +12644,7 @@
         <v>5485</v>
       </c>
       <c r="G305">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H305">
         <v>9</v>
@@ -12647,7 +12653,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>929</v>
       </c>
@@ -12667,7 +12673,7 @@
         <v>6925</v>
       </c>
       <c r="G306">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H306">
         <v>12</v>
@@ -12676,7 +12682,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>932</v>
       </c>
@@ -12696,7 +12702,7 @@
         <v>10085</v>
       </c>
       <c r="G307">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H307">
         <v>9</v>
@@ -12705,7 +12711,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>935</v>
       </c>
@@ -12725,7 +12731,7 @@
         <v>5235</v>
       </c>
       <c r="G308">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H308">
         <v>11</v>
@@ -12734,7 +12740,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>938</v>
       </c>
@@ -12754,7 +12760,7 @@
         <v>5310</v>
       </c>
       <c r="G309">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H309">
         <v>15</v>
@@ -12763,7 +12769,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>941</v>
       </c>
@@ -12783,7 +12789,7 @@
         <v>8220</v>
       </c>
       <c r="G310">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H310">
         <v>14</v>
@@ -12792,7 +12798,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>944</v>
       </c>
@@ -12812,7 +12818,7 @@
         <v>4760</v>
       </c>
       <c r="G311">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H311">
         <v>14</v>
@@ -12821,7 +12827,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>947</v>
       </c>
@@ -12841,7 +12847,7 @@
         <v>7480</v>
       </c>
       <c r="G312">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H312">
         <v>8</v>
@@ -12850,7 +12856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>950</v>
       </c>
@@ -12870,7 +12876,7 @@
         <v>1855</v>
       </c>
       <c r="G313">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H313">
         <v>12</v>
@@ -12879,7 +12885,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>953</v>
       </c>
@@ -12899,7 +12905,7 @@
         <v>7445</v>
       </c>
       <c r="G314">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H314">
         <v>14</v>
@@ -12908,7 +12914,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>956</v>
       </c>
@@ -12928,7 +12934,7 @@
         <v>680</v>
       </c>
       <c r="G315">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H315">
         <v>19</v>
@@ -12937,7 +12943,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>959</v>
       </c>
@@ -12957,7 +12963,7 @@
         <v>7170</v>
       </c>
       <c r="G316">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H316">
         <v>12</v>
@@ -12966,7 +12972,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>962</v>
       </c>
@@ -12986,7 +12992,7 @@
         <v>9030</v>
       </c>
       <c r="G317">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H317">
         <v>7</v>
@@ -12995,7 +13001,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>965</v>
       </c>
@@ -13015,7 +13021,7 @@
         <v>6515</v>
       </c>
       <c r="G318">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H318">
         <v>5</v>
@@ -13024,7 +13030,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>968</v>
       </c>
@@ -13044,7 +13050,7 @@
         <v>6490</v>
       </c>
       <c r="G319">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H319">
         <v>10</v>
@@ -13053,7 +13059,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>971</v>
       </c>
@@ -13073,7 +13079,7 @@
         <v>4790</v>
       </c>
       <c r="G320">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H320">
         <v>19</v>
@@ -13082,7 +13088,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>974</v>
       </c>
@@ -13102,7 +13108,7 @@
         <v>7145</v>
       </c>
       <c r="G321">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H321">
         <v>18</v>
@@ -13111,7 +13117,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>977</v>
       </c>
@@ -13131,7 +13137,7 @@
         <v>9120</v>
       </c>
       <c r="G322">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H322">
         <v>15</v>
@@ -13140,7 +13146,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>980</v>
       </c>
@@ -13160,7 +13166,7 @@
         <v>7380</v>
       </c>
       <c r="G323">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H323">
         <v>18</v>
@@ -13169,7 +13175,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>983</v>
       </c>
@@ -13189,7 +13195,7 @@
         <v>8755</v>
       </c>
       <c r="G324">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H324">
         <v>13</v>
@@ -13198,7 +13204,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>986</v>
       </c>
@@ -13218,7 +13224,7 @@
         <v>8300</v>
       </c>
       <c r="G325">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H325">
         <v>6</v>
@@ -13227,7 +13233,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>989</v>
       </c>
@@ -13247,7 +13253,7 @@
         <v>1550</v>
       </c>
       <c r="G326">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H326">
         <v>7</v>
@@ -13256,7 +13262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>993</v>
       </c>
@@ -13276,7 +13282,7 @@
         <v>585</v>
       </c>
       <c r="G327">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H327">
         <v>6</v>
@@ -13285,7 +13291,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>996</v>
       </c>
@@ -13305,7 +13311,7 @@
         <v>1715</v>
       </c>
       <c r="G328">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H328">
         <v>13</v>
@@ -13314,7 +13320,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>999</v>
       </c>
@@ -13334,7 +13340,7 @@
         <v>1245</v>
       </c>
       <c r="G329">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H329">
         <v>13</v>
@@ -13343,7 +13349,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>1002</v>
       </c>
@@ -13363,7 +13369,7 @@
         <v>1030</v>
       </c>
       <c r="G330">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H330">
         <v>14</v>
@@ -13372,7 +13378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>1005</v>
       </c>
@@ -13392,7 +13398,7 @@
         <v>2450</v>
       </c>
       <c r="G331">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H331">
         <v>19</v>
@@ -13401,7 +13407,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>1008</v>
       </c>
@@ -13421,7 +13427,7 @@
         <v>1555</v>
       </c>
       <c r="G332">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H332">
         <v>12</v>
@@ -13430,7 +13436,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>1011</v>
       </c>
@@ -13450,7 +13456,7 @@
         <v>1605</v>
       </c>
       <c r="G333">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H333">
         <v>7</v>
@@ -13459,7 +13465,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>1014</v>
       </c>
@@ -13479,7 +13485,7 @@
         <v>1725</v>
       </c>
       <c r="G334">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H334">
         <v>16</v>
@@ -13488,7 +13494,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>1017</v>
       </c>
@@ -13508,7 +13514,7 @@
         <v>2810</v>
       </c>
       <c r="G335">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H335">
         <v>14</v>
@@ -13517,7 +13523,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>1020</v>
       </c>
@@ -13537,7 +13543,7 @@
         <v>2540</v>
       </c>
       <c r="G336">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H336">
         <v>7</v>
@@ -13546,7 +13552,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>1023</v>
       </c>
@@ -13566,7 +13572,7 @@
         <v>300</v>
       </c>
       <c r="G337">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H337">
         <v>6</v>
@@ -13575,7 +13581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>1026</v>
       </c>
@@ -13595,7 +13601,7 @@
         <v>1440</v>
       </c>
       <c r="G338">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H338">
         <v>10</v>
@@ -13604,7 +13610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>1029</v>
       </c>
@@ -13624,7 +13630,7 @@
         <v>2050</v>
       </c>
       <c r="G339">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H339">
         <v>12</v>
@@ -13633,7 +13639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>1032</v>
       </c>
@@ -13653,7 +13659,7 @@
         <v>2170</v>
       </c>
       <c r="G340">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H340">
         <v>12</v>
@@ -13662,7 +13668,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>1035</v>
       </c>
@@ -13682,7 +13688,7 @@
         <v>995</v>
       </c>
       <c r="G341">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H341">
         <v>14</v>
@@ -13691,7 +13697,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>1038</v>
       </c>
@@ -13711,7 +13717,7 @@
         <v>4450</v>
       </c>
       <c r="G342">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H342">
         <v>13</v>
@@ -13720,7 +13726,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>1042</v>
       </c>
@@ -13740,7 +13746,7 @@
         <v>5765</v>
       </c>
       <c r="G343">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H343">
         <v>8</v>
@@ -13749,7 +13755,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>1045</v>
       </c>
@@ -13769,7 +13775,7 @@
         <v>885</v>
       </c>
       <c r="G344">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H344">
         <v>15</v>
@@ -13778,7 +13784,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>1048</v>
       </c>
@@ -13798,7 +13804,7 @@
         <v>1680</v>
       </c>
       <c r="G345">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H345">
         <v>19</v>
@@ -13807,7 +13813,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>1051</v>
       </c>
@@ -13827,7 +13833,7 @@
         <v>5835</v>
       </c>
       <c r="G346">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H346">
         <v>18</v>
@@ -13836,7 +13842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>1054</v>
       </c>
@@ -13856,7 +13862,7 @@
         <v>1125</v>
       </c>
       <c r="G347">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H347">
         <v>9</v>
@@ -13865,7 +13871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>1057</v>
       </c>
@@ -13885,7 +13891,7 @@
         <v>3550</v>
       </c>
       <c r="G348">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H348">
         <v>13</v>
@@ -13894,7 +13900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>1060</v>
       </c>
@@ -13914,7 +13920,7 @@
         <v>5945</v>
       </c>
       <c r="G349">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H349">
         <v>19</v>
@@ -13923,7 +13929,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>1063</v>
       </c>
@@ -13943,7 +13949,7 @@
         <v>5235</v>
       </c>
       <c r="G350">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H350">
         <v>15</v>
@@ -13952,7 +13958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>1066</v>
       </c>
@@ -13972,7 +13978,7 @@
         <v>1445</v>
       </c>
       <c r="G351">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H351">
         <v>15</v>
@@ -13981,7 +13987,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>1069</v>
       </c>
@@ -14001,7 +14007,7 @@
         <v>1245</v>
       </c>
       <c r="G352">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H352">
         <v>8</v>
@@ -14010,7 +14016,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>1072</v>
       </c>
@@ -14030,7 +14036,7 @@
         <v>1430</v>
       </c>
       <c r="G353">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H353">
         <v>17</v>
@@ -14039,7 +14045,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>1075</v>
       </c>
@@ -14059,7 +14065,7 @@
         <v>5040</v>
       </c>
       <c r="G354">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H354">
         <v>13</v>
@@ -14068,7 +14074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>1078</v>
       </c>
@@ -14088,7 +14094,7 @@
         <v>1295</v>
       </c>
       <c r="G355">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H355">
         <v>5</v>
@@ -14097,7 +14103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>1081</v>
       </c>
@@ -14117,7 +14123,7 @@
         <v>3885</v>
       </c>
       <c r="G356">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H356">
         <v>9</v>
@@ -14126,7 +14132,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>1084</v>
       </c>
@@ -14146,7 +14152,7 @@
         <v>645</v>
       </c>
       <c r="G357">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H357">
         <v>18</v>
@@ -14155,7 +14161,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>1087</v>
       </c>
@@ -14175,7 +14181,7 @@
         <v>1070</v>
       </c>
       <c r="G358">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H358">
         <v>8</v>
@@ -14184,7 +14190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>1090</v>
       </c>
@@ -14204,7 +14210,7 @@
         <v>5990</v>
       </c>
       <c r="G359">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H359">
         <v>16</v>
@@ -14213,7 +14219,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>1093</v>
       </c>
@@ -14233,7 +14239,7 @@
         <v>8760</v>
       </c>
       <c r="G360">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H360">
         <v>5</v>
@@ -14242,7 +14248,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1097</v>
       </c>
@@ -14262,7 +14268,7 @@
         <v>6685</v>
       </c>
       <c r="G361">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H361">
         <v>16</v>
@@ -14271,7 +14277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>1100</v>
       </c>
@@ -14291,7 +14297,7 @@
         <v>22195</v>
       </c>
       <c r="G362">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H362">
         <v>5</v>
@@ -14300,7 +14306,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>1103</v>
       </c>
@@ -14320,7 +14326,7 @@
         <v>6720</v>
       </c>
       <c r="G363">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H363">
         <v>13</v>
@@ -14329,7 +14335,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1106</v>
       </c>
@@ -14349,7 +14355,7 @@
         <v>21580</v>
       </c>
       <c r="G364">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H364">
         <v>7</v>
@@ -14358,7 +14364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>1109</v>
       </c>
@@ -14378,7 +14384,7 @@
         <v>26770</v>
       </c>
       <c r="G365">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H365">
         <v>11</v>
@@ -14387,7 +14393,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1112</v>
       </c>
@@ -14407,7 +14413,7 @@
         <v>7825</v>
       </c>
       <c r="G366">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H366">
         <v>14</v>
@@ -14416,7 +14422,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1115</v>
       </c>
@@ -14436,7 +14442,7 @@
         <v>5750</v>
       </c>
       <c r="G367">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H367">
         <v>7</v>
@@ -14445,7 +14451,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>1118</v>
       </c>
@@ -14465,7 +14471,7 @@
         <v>5540</v>
       </c>
       <c r="G368">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H368">
         <v>10</v>
@@ -14474,7 +14480,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>1121</v>
       </c>
@@ -14494,7 +14500,7 @@
         <v>13660</v>
       </c>
       <c r="G369">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H369">
         <v>18</v>
@@ -14503,7 +14509,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>1124</v>
       </c>
@@ -14523,7 +14529,7 @@
         <v>8235</v>
       </c>
       <c r="G370">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H370">
         <v>13</v>
@@ -14532,7 +14538,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1127</v>
       </c>
@@ -14552,7 +14558,7 @@
         <v>14100</v>
       </c>
       <c r="G371">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H371">
         <v>16</v>
@@ -14561,7 +14567,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>1130</v>
       </c>
@@ -14581,7 +14587,7 @@
         <v>15755</v>
       </c>
       <c r="G372">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="H372">
         <v>18</v>
@@ -14592,6 +14598,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>